--- a/research/traditional_assets/database/data/nigeria/nigeria_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.172</v>
+        <v>0.148</v>
       </c>
       <c r="E2">
-        <v>0.14</v>
+        <v>0.188</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>25.2</v>
+        <v>30.1</v>
       </c>
       <c r="L2">
-        <v>0.6043165467625898</v>
+        <v>0.6825396825396826</v>
       </c>
       <c r="M2">
-        <v>10.2</v>
+        <v>20.8</v>
       </c>
       <c r="N2">
-        <v>0.07088255733148019</v>
+        <v>0.1109333333333333</v>
       </c>
       <c r="O2">
-        <v>0.4047619047619048</v>
+        <v>0.6910299003322259</v>
       </c>
       <c r="P2">
-        <v>10.2</v>
+        <v>20.8</v>
       </c>
       <c r="Q2">
-        <v>0.07088255733148019</v>
+        <v>0.1109333333333333</v>
       </c>
       <c r="R2">
-        <v>0.4047619047619048</v>
+        <v>0.6910299003322259</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>210.2</v>
+        <v>529.4</v>
       </c>
       <c r="V2">
-        <v>1.460736622654621</v>
+        <v>2.823466666666667</v>
       </c>
       <c r="W2">
-        <v>0.48</v>
+        <v>0.4588414634146342</v>
       </c>
       <c r="X2">
-        <v>0.09633514661429998</v>
+        <v>0.1746392812666896</v>
       </c>
       <c r="Y2">
-        <v>0.3836648533857</v>
+        <v>0.2842021821479446</v>
       </c>
       <c r="Z2">
-        <v>-0.4312306101344364</v>
+        <v>1.122137404580152</v>
       </c>
       <c r="AA2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07165995669886743</v>
+        <v>0.1347230127400922</v>
       </c>
       <c r="AC2">
-        <v>-0.07165995669886743</v>
+        <v>-0.1347230127400922</v>
       </c>
       <c r="AD2">
-        <v>183.9</v>
+        <v>197.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>183.9</v>
+        <v>197.5</v>
       </c>
       <c r="AG2">
-        <v>-26.29999999999998</v>
+        <v>-331.9</v>
       </c>
       <c r="AH2">
-        <v>0.5610128126906651</v>
+        <v>0.512987012987013</v>
       </c>
       <c r="AI2">
-        <v>0.7370741482965932</v>
+        <v>0.7422021796317173</v>
       </c>
       <c r="AJ2">
-        <v>-0.2236394557823127</v>
+        <v>2.298476454293629</v>
       </c>
       <c r="AK2">
-        <v>-0.6692111959287526</v>
+        <v>1.260539308773263</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.172</v>
+        <v>0.148</v>
       </c>
       <c r="E3">
-        <v>0.14</v>
+        <v>0.188</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>25.2</v>
+        <v>30.1</v>
       </c>
       <c r="L3">
-        <v>0.6043165467625898</v>
+        <v>0.6825396825396826</v>
       </c>
       <c r="M3">
-        <v>10.2</v>
+        <v>20.8</v>
       </c>
       <c r="N3">
-        <v>0.07088255733148019</v>
+        <v>0.1109333333333333</v>
       </c>
       <c r="O3">
-        <v>0.4047619047619048</v>
+        <v>0.6910299003322259</v>
       </c>
       <c r="P3">
-        <v>10.2</v>
+        <v>20.8</v>
       </c>
       <c r="Q3">
-        <v>0.07088255733148019</v>
+        <v>0.1109333333333333</v>
       </c>
       <c r="R3">
-        <v>0.4047619047619048</v>
+        <v>0.6910299003322259</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>210.2</v>
+        <v>529.4</v>
       </c>
       <c r="V3">
-        <v>1.460736622654621</v>
+        <v>2.823466666666667</v>
       </c>
       <c r="W3">
-        <v>0.48</v>
+        <v>0.4588414634146342</v>
       </c>
       <c r="X3">
-        <v>0.09633514661429998</v>
+        <v>0.1746392812666896</v>
       </c>
       <c r="Y3">
-        <v>0.3836648533857</v>
+        <v>0.2842021821479446</v>
       </c>
       <c r="Z3">
-        <v>-0.4312306101344364</v>
+        <v>1.122137404580152</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07165995669886743</v>
+        <v>0.1347230127400922</v>
       </c>
       <c r="AC3">
-        <v>-0.07165995669886743</v>
+        <v>-0.1347230127400922</v>
       </c>
       <c r="AD3">
-        <v>183.9</v>
+        <v>197.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>183.9</v>
+        <v>197.5</v>
       </c>
       <c r="AG3">
-        <v>-26.29999999999998</v>
+        <v>-331.9</v>
       </c>
       <c r="AH3">
-        <v>0.5610128126906651</v>
+        <v>0.512987012987013</v>
       </c>
       <c r="AI3">
-        <v>0.7370741482965932</v>
+        <v>0.7422021796317173</v>
       </c>
       <c r="AJ3">
-        <v>-0.2236394557823127</v>
+        <v>2.298476454293629</v>
       </c>
       <c r="AK3">
-        <v>-0.6692111959287526</v>
+        <v>1.260539308773263</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/nigeria/nigeria_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_brokerage_investment_banking.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.148</v>
+        <v>0.129</v>
       </c>
       <c r="E2">
-        <v>0.188</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.04695945945945947</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>-0.04695945945945947</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-0.3783783783783784</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-0.2210948236371965</v>
       </c>
       <c r="K2">
-        <v>30.1</v>
+        <v>1.38</v>
       </c>
       <c r="L2">
-        <v>0.6825396825396826</v>
+        <v>0.4662162162162162</v>
       </c>
       <c r="M2">
-        <v>20.8</v>
+        <v>1.28</v>
       </c>
       <c r="N2">
-        <v>0.1109333333333333</v>
+        <v>0.07664670658682635</v>
       </c>
       <c r="O2">
-        <v>0.6910299003322259</v>
+        <v>0.9275362318840581</v>
       </c>
       <c r="P2">
-        <v>20.8</v>
+        <v>1.28</v>
       </c>
       <c r="Q2">
-        <v>0.1109333333333333</v>
+        <v>0.07664670658682635</v>
       </c>
       <c r="R2">
-        <v>0.6910299003322259</v>
+        <v>0.9275362318840581</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>529.4</v>
+        <v>12.1</v>
       </c>
       <c r="V2">
-        <v>2.823466666666667</v>
+        <v>0.7245508982035929</v>
       </c>
       <c r="W2">
-        <v>0.4588414634146342</v>
+        <v>0.0660287081339713</v>
       </c>
       <c r="X2">
-        <v>0.1746392812666896</v>
+        <v>0.09909241799323454</v>
       </c>
       <c r="Y2">
-        <v>0.2842021821479446</v>
+        <v>-0.03306370985926324</v>
       </c>
       <c r="Z2">
-        <v>1.122137404580152</v>
+        <v>0.1672221908366759</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>-0.03697196079126048</v>
       </c>
       <c r="AB2">
-        <v>0.1347230127400922</v>
+        <v>0.09908949479672995</v>
       </c>
       <c r="AC2">
-        <v>-0.1347230127400922</v>
+        <v>-0.1360614555879904</v>
       </c>
       <c r="AD2">
-        <v>197.5</v>
+        <v>0.011</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>197.5</v>
+        <v>0.011</v>
       </c>
       <c r="AG2">
-        <v>-331.9</v>
+        <v>-12.089</v>
       </c>
       <c r="AH2">
-        <v>0.512987012987013</v>
+        <v>0.0006582490575070313</v>
       </c>
       <c r="AI2">
-        <v>0.7422021796317173</v>
+        <v>0.0009235160775753505</v>
       </c>
       <c r="AJ2">
-        <v>2.298476454293629</v>
+        <v>-2.621774018651053</v>
       </c>
       <c r="AK2">
-        <v>1.260539308773263</v>
+        <v>63.96296296296295</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-3.469</v>
+      </c>
+      <c r="AN2">
+        <v>-0.01057692307692308</v>
+      </c>
+      <c r="AO2">
+        <v>-1120</v>
+      </c>
+      <c r="AP2">
+        <v>11.62403846153846</v>
+      </c>
+      <c r="AQ2">
+        <v>0.3228596137215336</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>United Capital Plc (NGSE:UCAP)</t>
+          <t>Africa Prudential Plc (NGSE:AFRIPRUD)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.148</v>
+        <v>0.129</v>
       </c>
       <c r="E3">
-        <v>0.188</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-0.04695945945945947</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>-0.04695945945945947</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-0.3783783783783784</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>-0.2210948236371965</v>
       </c>
       <c r="K3">
-        <v>30.1</v>
+        <v>1.38</v>
       </c>
       <c r="L3">
-        <v>0.6825396825396826</v>
+        <v>0.4662162162162162</v>
       </c>
       <c r="M3">
-        <v>20.8</v>
+        <v>1.28</v>
       </c>
       <c r="N3">
-        <v>0.1109333333333333</v>
+        <v>0.07664670658682635</v>
       </c>
       <c r="O3">
-        <v>0.6910299003322259</v>
+        <v>0.9275362318840581</v>
       </c>
       <c r="P3">
-        <v>20.8</v>
+        <v>1.28</v>
       </c>
       <c r="Q3">
-        <v>0.1109333333333333</v>
+        <v>0.07664670658682635</v>
       </c>
       <c r="R3">
-        <v>0.6910299003322259</v>
+        <v>0.9275362318840581</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,61 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>529.4</v>
+        <v>12.1</v>
       </c>
       <c r="V3">
-        <v>2.823466666666667</v>
+        <v>0.7245508982035929</v>
       </c>
       <c r="W3">
-        <v>0.4588414634146342</v>
+        <v>0.0660287081339713</v>
       </c>
       <c r="X3">
-        <v>0.1746392812666896</v>
+        <v>0.09909241799323454</v>
       </c>
       <c r="Y3">
-        <v>0.2842021821479446</v>
+        <v>-0.03306370985926324</v>
       </c>
       <c r="Z3">
-        <v>1.122137404580152</v>
+        <v>0.1672221908366759</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>-0.03697196079126048</v>
       </c>
       <c r="AB3">
-        <v>0.1347230127400922</v>
+        <v>0.09908949479672995</v>
       </c>
       <c r="AC3">
-        <v>-0.1347230127400922</v>
+        <v>-0.1360614555879904</v>
       </c>
       <c r="AD3">
-        <v>197.5</v>
+        <v>0.011</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>197.5</v>
+        <v>0.011</v>
       </c>
       <c r="AG3">
-        <v>-331.9</v>
+        <v>-12.089</v>
       </c>
       <c r="AH3">
-        <v>0.512987012987013</v>
+        <v>0.0006582490575070313</v>
       </c>
       <c r="AI3">
-        <v>0.7422021796317173</v>
+        <v>0.0009235160775753505</v>
       </c>
       <c r="AJ3">
-        <v>2.298476454293629</v>
+        <v>-2.621774018651053</v>
       </c>
       <c r="AK3">
-        <v>1.260539308773263</v>
+        <v>63.96296296296295</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-3.469</v>
+      </c>
+      <c r="AN3">
+        <v>-0.01057692307692308</v>
+      </c>
+      <c r="AO3">
+        <v>-1120</v>
+      </c>
+      <c r="AP3">
+        <v>11.62403846153846</v>
+      </c>
+      <c r="AQ3">
+        <v>0.3228596137215336</v>
       </c>
     </row>
   </sheetData>
